--- a/ru/downloads/data-excel/7.b.1.1.xlsx
+++ b/ru/downloads/data-excel/7.b.1.1.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\korozbaeva\Desktop\Показатели ЦУР для Платформы\Национальные показатели ЦУР\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="R:\Показатели ЦУР для Платформы\Национальные показатели ЦУР — 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF148386-A854-41CB-AFAB-BFDFF51B6123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="1170" yWindow="1170" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="7.b.1.1a" sheetId="1" r:id="rId1"/>
@@ -20,14 +21,6 @@
     <definedName name="Button_2">"Pokreal_CHC_List"</definedName>
   </definedNames>
   <calcPr calcId="152511"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -76,7 +69,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0.0"/>
     <numFmt numFmtId="165" formatCode="_-* #,##0.0000_р_._-;\-* #,##0.0000_р_._-;_-* &quot;-&quot;????_р_._-;_-@_-"/>
@@ -237,7 +230,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -248,10 +241,10 @@
     </xf>
   </cellXfs>
   <cellStyles count="5">
-    <cellStyle name="Normal 17" xfId="2"/>
-    <cellStyle name="Normal 2" xfId="4"/>
+    <cellStyle name="Normal 17" xfId="2" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
+    <cellStyle name="Normal 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 7" xfId="3"/>
+    <cellStyle name="Обычный 7" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="Финансовый" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -268,9 +261,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Тема Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Стандартная">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -308,9 +301,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Стандартная">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -345,7 +338,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -380,7 +373,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Стандартная">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -553,9 +546,9 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Лист4"/>
-  <dimension ref="A1:T1022"/>
+  <dimension ref="A1:U1022"/>
   <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="3" width="37.42578125" style="2" customWidth="1"/>
@@ -563,7 +556,7 @@
     <col min="21" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:21" ht="72.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
         <v>3</v>
       </c>
@@ -574,7 +567,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="20" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" s="20" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="19" t="s">
         <v>12</v>
       </c>
@@ -585,11 +578,11 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:20" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B3" s="4"/>
       <c r="C3" s="4"/>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="17" t="s">
         <v>4</v>
       </c>
@@ -650,8 +643,11 @@
       <c r="T4" s="1">
         <v>2023</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="U4" s="1">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>8</v>
       </c>
@@ -712,65 +708,68 @@
       <c r="T5" s="16">
         <v>1.2E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U5" s="16">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B6" s="10"/>
       <c r="C6" s="10"/>
       <c r="D6" s="10"/>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B7" s="10"/>
       <c r="C7" s="10"/>
       <c r="D7" s="10"/>
       <c r="O7" s="11"/>
       <c r="P7" s="11"/>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B8" s="10"/>
       <c r="C8" s="10"/>
       <c r="D8" s="10"/>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B9" s="10"/>
       <c r="C9" s="10"/>
       <c r="D9" s="10"/>
     </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B10" s="10"/>
       <c r="C10" s="10"/>
       <c r="D10" s="10"/>
       <c r="Q10" s="12"/>
     </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B11" s="10"/>
       <c r="C11" s="10"/>
       <c r="D11" s="10"/>
     </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B12" s="10"/>
       <c r="C12" s="10"/>
       <c r="D12" s="10"/>
     </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B13" s="10"/>
       <c r="C13" s="10"/>
       <c r="D13" s="10"/>
       <c r="O13" s="13"/>
       <c r="P13" s="13"/>
     </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
       <c r="D14" s="10"/>
       <c r="O14" s="14"/>
       <c r="P14" s="15"/>
     </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B15" s="10"/>
       <c r="C15" s="10"/>
       <c r="D15" s="10"/>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
       <c r="B16" s="10"/>
       <c r="C16" s="10"/>
       <c r="D16" s="10"/>
